--- a/files/me-ADPER9002586012.xlsx
+++ b/files/me-ADPER9002586012.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -573,40 +573,40 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
+          <t>Development and utilization of agricultural and rural climate information systems to respond to climate crisis</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
+          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>59-70</t>
+          <t>1129-1139</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.3.059</t>
+          <t>10.15531/ksccr.2025.16.5.1129</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -616,6 +616,59 @@
       </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59-70</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2025.67.3.059</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
